--- a/dataset/Non-Faulty/dead_lock.xlsx
+++ b/dataset/Non-Faulty/dead_lock.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/dead_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/dead_lock.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/dead_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/dead_lock.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,19 +473,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pthread_mutex_t dead_lock_001_glb_mutexA = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_001_glb_mutexB = PTHREAD_MUTEX_INITIALIZER; int dead_lock_001_glb_dataA = 10; int dead_lock_001_glb_dataB = 10; pthread_mutex_t dead_lock_002_glb_mutexA = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_002_glb_mutexB = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_002_glb_mutexC = PTHREAD_MUTEX_INITIALIZER; int dead_lock_002_glb_dataA = 0; int dead_lock_002_glb_dataB = 0; int dead_lock_002_glb_dataC = 0; pthread_mutex_t dead_lock_003_glb_mutexA_; pthread_mutex_t dead_lock_003_glb_mutexB_; pthread_mutex_t dead_lock_003_glb_mutexC_; pthread_mutex_t *dead_lock_003_glb_mutexA = &amp;dead_lock_003_glb_mutexA_; pthread_mutex_t *dead_lock_003_glb_mutexB = &amp;dead_lock_003_glb_mutexB_; pthread_mutex_t *dead_lock_003_glb_mutexC = &amp;dead_lock_003_glb_mutexC_; int dead_lock_003_glb_dataA = 0; int dead_lock_003_glb_dataB = 0; int dead_lock_003_glb_dataC = 0; pthread_mutex_t dead_lock_004_glb_mutexA_; pthread_mutex_t dead_lock_004_glb_mutexB_; pthread_mutex_t dead_lock_004_glb_mutexC_; pthread_mutex_t *dead_lock_004_glb_mutexA = &amp;dead_lock_004_glb_mutexA_; pthread_mutex_t *dead_lock_004_glb_mutexB = &amp;dead_lock_004_glb_mutexB_; pthread_mutex_t *dead_lock_004_glb_mutexC = &amp;dead_lock_004_glb_mutexC_; int dead_lock_004_glb_dataA = 0; int dead_lock_004_glb_dataB = 0; int dead_lock_004_glb_dataC = 0; pthread_mutex_t dead_lock_005_glb_mutexA_; pthread_mutex_t dead_lock_005_glb_mutexB_; pthread_mutex_t *dead_lock_005_glb_mutexA = &amp;dead_lock_005_glb_mutexA_; pthread_mutex_t *dead_lock_005_glb_mutexB = &amp;dead_lock_005_glb_mutexB_; int dead_lock_005_glb_dataA = 0; int dead_lock_005_glb_dataB = 0; extern volatile int vflag; void dead_lock_002 () { pthread_t tid1; pthread_t tid2; pthread_t tid3; pthread_mutex_init(&amp;dead_lock_002_glb_mutexA, NULL); pthread_mutex_init(&amp;dead_lock_002_glb_mutexB, NULL); pthread_mutex_init(&amp;dead_lock_002_glb_mutexC, NULL); pthread_create(&amp;tid1, NULL, dead_lock_002_tsk_001, NULL); pthread_create(&amp;tid2, NULL, dead_lock_002_tsk_002, NULL); pthread_create(&amp;tid3, NULL, dead_lock_002_tsk_003, NULL); pthread_join(tid1, NULL); pthread_join(tid2, NULL); pthread_join(tid3, NULL); pthread_mutex_destroy(&amp;dead_lock_002_glb_mutexA); pthread_mutex_destroy(&amp;dead_lock_002_glb_mutexB); pthread_mutex_destroy(&amp;dead_lock_002_glb_mutexC); } void* dead_lock_002_tsk_002 (void *pram) { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexB); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataB = (dead_lock_002_glb_dataB % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexC); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataC = (dead_lock_002_glb_dataC % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexC); #endif /* ! defined(CHECKER_POLYSPACE) */ #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexB); #endif /* ! defined(CHECKER_POLYSPACE) */ return NULL; } void* dead_lock_002_tsk_003 (void *pram) { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexA); /*Tool should Not detect this line as error*/ /*No ERROR:Dead Lock*/ #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataA = (dead_lock_002_glb_dataA % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexC); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataC = (dead_lock_002_glb_dataC % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexC); #endif /* ! defined(CHECKER_POLYSPACE) */ #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexA); #endif /* ! defined(CHECKER_POLYSPACE) */ return NULL; } void* dead_lock_002_tsk_001 (void *pram) { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexA); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataA = (dead_lock_002_glb_dataA % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexB); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataB = (dead_lock_002_glb_dataB % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexB); #endif /* ! defined(CHECKER_POLYSPACE) */ #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexA); #endif /* ! defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>pthread_mutex_t dead_lock_001_glb_mutexA = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_001_glb_mutexB = PTHREAD_MUTEX_INITIALIZER; int dead_lock_001_glb_dataA = 10; int dead_lock_001_glb_dataB = 10; pthread_mutex_t dead_lock_002_glb_mutexA = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_002_glb_mutexB = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_002_glb_mutexC = PTHREAD_MUTEX_INITIALIZER; int dead_lock_002_glb_dataA = 0; int dead_lock_002_glb_dataB = 0; int dead_lock_002_glb_dataC = 0; pthread_mutex_t dead_lock_003_glb_mutexA_; pthread_mutex_t dead_lock_003_glb_mutexB_; pthread_mutex_t dead_lock_003_glb_mutexC_; pthread_mutex_t *dead_lock_003_glb_mutexA = &amp;dead_lock_003_glb_mutexA_; pthread_mutex_t *dead_lock_003_glb_mutexB = &amp;dead_lock_003_glb_mutexB_; pthread_mutex_t *dead_lock_003_glb_mutexC = &amp;dead_lock_003_glb_mutexC_; int dead_lock_003_glb_dataA = 0; int dead_lock_003_glb_dataB = 0; int dead_lock_003_glb_dataC = 0; pthread_mutex_t dead_lock_004_glb_mutexA_; pthread_mutex_t dead_lock_004_glb_mutexB_; pthread_mutex_t dead_lock_004_glb_mutexC_; pthread_mutex_t *dead_lock_004_glb_mutexA = &amp;dead_lock_004_glb_mutexA_; pthread_mutex_t *dead_lock_004_glb_mutexB = &amp;dead_lock_004_glb_mutexB_; pthread_mutex_t *dead_lock_004_glb_mutexC = &amp;dead_lock_004_glb_mutexC_; int dead_lock_004_glb_dataA = 0; int dead_lock_004_glb_dataB = 0; int dead_lock_004_glb_dataC = 0; pthread_mutex_t dead_lock_005_glb_mutexA_; pthread_mutex_t dead_lock_005_glb_mutexB_; pthread_mutex_t *dead_lock_005_glb_mutexA = &amp;dead_lock_005_glb_mutexA_; pthread_mutex_t *dead_lock_005_glb_mutexB = &amp;dead_lock_005_glb_mutexB_; int dead_lock_005_glb_dataA = 0; int dead_lock_005_glb_dataB = 0; extern volatile int vflag; void dead_lock_002 () { pthread_t tid1; pthread_t tid2; pthread_t tid3; pthread_mutex_init(&amp;dead_lock_002_glb_mutexA, NULL); pthread_mutex_init(&amp;dead_lock_002_glb_mutexB, NULL); pthread_mutex_init(&amp;dead_lock_002_glb_mutexC, NULL); pthread_create(&amp;tid1, NULL, dead_lock_002_tsk_001, NULL); pthread_create(&amp;tid2, NULL, dead_lock_002_tsk_002, NULL); pthread_create(&amp;tid3, NULL, dead_lock_002_tsk_003, NULL); pthread_join(tid1, NULL); pthread_join(tid2, NULL); pthread_join(tid3, NULL); pthread_mutex_destroy(&amp;dead_lock_002_glb_mutexA); pthread_mutex_destroy(&amp;dead_lock_002_glb_mutexB); pthread_mutex_destroy(&amp;dead_lock_002_glb_mutexC); } void* dead_lock_002_tsk_003 (void *pram) { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexA); /*Tool should Not detect this line as error*/ /*No ERROR:Dead Lock*/ #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataA = (dead_lock_002_glb_dataA % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexC); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataC = (dead_lock_002_glb_dataC % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexC); #endif /* ! defined(CHECKER_POLYSPACE) */ #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexA); #endif /* ! defined(CHECKER_POLYSPACE) */ return NULL; } void* dead_lock_002_tsk_002 (void *pram) { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexB); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataB = (dead_lock_002_glb_dataB % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexC); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataC = (dead_lock_002_glb_dataC % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexC); #endif /* ! defined(CHECKER_POLYSPACE) */ #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexB); #endif /* ! defined(CHECKER_POLYSPACE) */ return NULL; } void* dead_lock_002_tsk_001 (void *pram) { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexA); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataA = (dead_lock_002_glb_dataA % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(&amp;dead_lock_002_glb_mutexB); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_002_glb_dataB = (dead_lock_002_glb_dataB % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexB); #endif /* ! defined(CHECKER_POLYSPACE) */ #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(&amp;dead_lock_002_glb_mutexA); #endif /* ! defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/dead_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/dead_lock.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/dead_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/dead_lock.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/dead_lock.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/dead_lock.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pthread_mutex_t dead_lock_001_glb_mutexA = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_001_glb_mutexB = PTHREAD_MUTEX_INITIALIZER; int dead_lock_001_glb_dataA = 10; int dead_lock_001_glb_dataB = 10; pthread_mutex_t dead_lock_002_glb_mutexA = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_002_glb_mutexB = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_002_glb_mutexC = PTHREAD_MUTEX_INITIALIZER; int dead_lock_002_glb_dataA = 0; int dead_lock_002_glb_dataB = 0; int dead_lock_002_glb_dataC = 0; pthread_mutex_t dead_lock_003_glb_mutexA_; pthread_mutex_t dead_lock_003_glb_mutexB_; pthread_mutex_t dead_lock_003_glb_mutexC_; pthread_mutex_t *dead_lock_003_glb_mutexA = &amp;dead_lock_003_glb_mutexA_; pthread_mutex_t *dead_lock_003_glb_mutexB = &amp;dead_lock_003_glb_mutexB_; pthread_mutex_t *dead_lock_003_glb_mutexC = &amp;dead_lock_003_glb_mutexC_; int dead_lock_003_glb_dataA = 0; int dead_lock_003_glb_dataB = 0; int dead_lock_003_glb_dataC = 0; pthread_mutex_t dead_lock_004_glb_mutexA_; pthread_mutex_t dead_lock_004_glb_mutexB_; pthread_mutex_t dead_lock_004_glb_mutexC_; pthread_mutex_t *dead_lock_004_glb_mutexA = &amp;dead_lock_004_glb_mutexA_; pthread_mutex_t *dead_lock_004_glb_mutexB = &amp;dead_lock_004_glb_mutexB_; pthread_mutex_t *dead_lock_004_glb_mutexC = &amp;dead_lock_004_glb_mutexC_; int dead_lock_004_glb_dataA = 0; int dead_lock_004_glb_dataB = 0; int dead_lock_004_glb_dataC = 0; pthread_mutex_t dead_lock_005_glb_mutexA_; pthread_mutex_t dead_lock_005_glb_mutexB_; pthread_mutex_t *dead_lock_005_glb_mutexA = &amp;dead_lock_005_glb_mutexA_; pthread_mutex_t *dead_lock_005_glb_mutexB = &amp;dead_lock_005_glb_mutexB_; int dead_lock_005_glb_dataA = 0; int dead_lock_005_glb_dataB = 0; extern volatile int vflag; void dead_lock_005 () { pthread_t tid1; pthread_t tid2; pthread_mutex_init(dead_lock_005_glb_mutexA, NULL); pthread_mutex_init(dead_lock_005_glb_mutexB, NULL); pthread_create(&amp;tid1, NULL, dead_lock_005_tsk_001, NULL); pthread_create(&amp;tid2, NULL, dead_lock_005_tsk_002, NULL); pthread_join(tid1, NULL); pthread_join(tid2, NULL); pthread_mutex_destroy(dead_lock_005_glb_mutexA); pthread_mutex_destroy(dead_lock_005_glb_mutexB); } void* dead_lock_005_tsk_001 (void *pram) { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(dead_lock_005_glb_mutexA); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_lock(&amp;dead_lock_005_glb_mutexA_); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_005_glb_dataA = (dead_lock_005_glb_dataA % 100) + 1; dead_lock_005_func_001(); #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(dead_lock_005_glb_mutexA); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_unlock(&amp;dead_lock_005_glb_mutexA_); #endif /* ! defined(CHECKER_POLYSPACE) */ return NULL; } void dead_lock_005_func_001 () { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(dead_lock_005_glb_mutexB); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_lock(&amp;dead_lock_005_glb_mutexB_); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_005_glb_dataB = (dead_lock_005_glb_dataB % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(dead_lock_005_glb_mutexB); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_unlock(&amp;dead_lock_005_glb_mutexB_); #endif /* ! defined(CHECKER_POLYSPACE) */ } void* dead_lock_005_tsk_002 (void *pram) { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(dead_lock_005_glb_mutexA); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_lock(&amp;dead_lock_005_glb_mutexA_); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_005_glb_dataA = (dead_lock_005_glb_dataA % 100) + 1; dead_lock_005_func_002(); #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(dead_lock_005_glb_mutexA); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_unlock(&amp;dead_lock_005_glb_mutexA_); #endif /* ! defined(CHECKER_POLYSPACE) */ return NULL; } void dead_lock_005_func_002 () { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(dead_lock_005_glb_mutexB); /*Tool should Not detect this line as error*/ /*No ERROR:Dead Lock*/ #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_lock(&amp;dead_lock_005_glb_mutexB_); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_005_glb_dataB = (dead_lock_005_glb_dataB % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(dead_lock_005_glb_mutexB); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_unlock(&amp;dead_lock_005_glb_mutexB_); #endif /* ! defined(CHECKER_POLYSPACE) */ }</t>
+          <t>pthread_mutex_t dead_lock_001_glb_mutexA = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_001_glb_mutexB = PTHREAD_MUTEX_INITIALIZER; int dead_lock_001_glb_dataA = 10; int dead_lock_001_glb_dataB = 10; pthread_mutex_t dead_lock_002_glb_mutexA = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_002_glb_mutexB = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t dead_lock_002_glb_mutexC = PTHREAD_MUTEX_INITIALIZER; int dead_lock_002_glb_dataA = 0; int dead_lock_002_glb_dataB = 0; int dead_lock_002_glb_dataC = 0; pthread_mutex_t dead_lock_003_glb_mutexA_; pthread_mutex_t dead_lock_003_glb_mutexB_; pthread_mutex_t dead_lock_003_glb_mutexC_; pthread_mutex_t *dead_lock_003_glb_mutexA = &amp;dead_lock_003_glb_mutexA_; pthread_mutex_t *dead_lock_003_glb_mutexB = &amp;dead_lock_003_glb_mutexB_; pthread_mutex_t *dead_lock_003_glb_mutexC = &amp;dead_lock_003_glb_mutexC_; int dead_lock_003_glb_dataA = 0; int dead_lock_003_glb_dataB = 0; int dead_lock_003_glb_dataC = 0; pthread_mutex_t dead_lock_004_glb_mutexA_; pthread_mutex_t dead_lock_004_glb_mutexB_; pthread_mutex_t dead_lock_004_glb_mutexC_; pthread_mutex_t *dead_lock_004_glb_mutexA = &amp;dead_lock_004_glb_mutexA_; pthread_mutex_t *dead_lock_004_glb_mutexB = &amp;dead_lock_004_glb_mutexB_; pthread_mutex_t *dead_lock_004_glb_mutexC = &amp;dead_lock_004_glb_mutexC_; int dead_lock_004_glb_dataA = 0; int dead_lock_004_glb_dataB = 0; int dead_lock_004_glb_dataC = 0; pthread_mutex_t dead_lock_005_glb_mutexA_; pthread_mutex_t dead_lock_005_glb_mutexB_; pthread_mutex_t *dead_lock_005_glb_mutexA = &amp;dead_lock_005_glb_mutexA_; pthread_mutex_t *dead_lock_005_glb_mutexB = &amp;dead_lock_005_glb_mutexB_; int dead_lock_005_glb_dataA = 0; int dead_lock_005_glb_dataB = 0; extern volatile int vflag; void dead_lock_005 () { pthread_t tid1; pthread_t tid2; pthread_mutex_init(dead_lock_005_glb_mutexA, NULL); pthread_mutex_init(dead_lock_005_glb_mutexB, NULL); pthread_create(&amp;tid1, NULL, dead_lock_005_tsk_001, NULL); pthread_create(&amp;tid2, NULL, dead_lock_005_tsk_002, NULL); pthread_join(tid1, NULL); pthread_join(tid2, NULL); pthread_mutex_destroy(dead_lock_005_glb_mutexA); pthread_mutex_destroy(dead_lock_005_glb_mutexB); } void* dead_lock_005_tsk_002 (void *pram) { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(dead_lock_005_glb_mutexA); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_lock(&amp;dead_lock_005_glb_mutexA_); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_005_glb_dataA = (dead_lock_005_glb_dataA % 100) + 1; dead_lock_005_func_002(); #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(dead_lock_005_glb_mutexA); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_unlock(&amp;dead_lock_005_glb_mutexA_); #endif /* ! defined(CHECKER_POLYSPACE) */ return NULL; } void dead_lock_005_func_002 () { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(dead_lock_005_glb_mutexB); /*Tool should Not detect this line as error*/ /*No ERROR:Dead Lock*/ #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_lock(&amp;dead_lock_005_glb_mutexB_); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_005_glb_dataB = (dead_lock_005_glb_dataB % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(dead_lock_005_glb_mutexB); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_unlock(&amp;dead_lock_005_glb_mutexB_); #endif /* ! defined(CHECKER_POLYSPACE) */ } void* dead_lock_005_tsk_001 (void *pram) { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(dead_lock_005_glb_mutexA); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_lock(&amp;dead_lock_005_glb_mutexA_); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_005_glb_dataA = (dead_lock_005_glb_dataA % 100) + 1; dead_lock_005_func_001(); #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(dead_lock_005_glb_mutexA); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_unlock(&amp;dead_lock_005_glb_mutexA_); #endif /* ! defined(CHECKER_POLYSPACE) */ return NULL; } void dead_lock_005_func_001 () { #if ! defined(CHECKER_POLYSPACE) pthread_mutex_lock(dead_lock_005_glb_mutexB); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_lock(&amp;dead_lock_005_glb_mutexB_); #endif /* ! defined(CHECKER_POLYSPACE) */ dead_lock_005_glb_dataB = (dead_lock_005_glb_dataB % 100) + 1; #if ! defined(CHECKER_POLYSPACE) pthread_mutex_unlock(dead_lock_005_glb_mutexB); #else /* ! defined(CHECKER_POLYSPACE) */ pthread_mutex_unlock(&amp;dead_lock_005_glb_mutexB_); #endif /* ! defined(CHECKER_POLYSPACE) */ }</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
